--- a/frame_distill_results.xlsx
+++ b/frame_distill_results.xlsx
@@ -1013,11 +1013,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fighting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.4246856868267059</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="23">
@@ -1040,11 +1040,11 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fighting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.3223377168178558</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="24">
@@ -1067,11 +1067,11 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.3483579754829407</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="25">
@@ -1094,11 +1094,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.3483579754829407</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="26">
@@ -1121,11 +1121,11 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.3483579754829407</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="27">
@@ -1148,11 +1148,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.3483579754829407</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="28">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.3483579754829407</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="29">
@@ -1202,11 +1202,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.3483579754829407</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="30">
@@ -1229,11 +1229,11 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.3483579754829407</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="31">
@@ -1256,11 +1256,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.3483579754829407</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="32">
@@ -1283,11 +1283,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.2531600892543793</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="33">
@@ -1310,11 +1310,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.2587009072303772</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="34">
@@ -1337,11 +1337,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.2283122837543488</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="35">
@@ -1364,11 +1364,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.2997436821460724</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="36">
@@ -1391,11 +1391,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.2377611696720123</v>
+        <v>0.9622158227779068</v>
       </c>
     </row>
     <row r="37">
@@ -1418,11 +1418,11 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.377488762140274</v>
+        <v>0.9891004681216021</v>
       </c>
     </row>
     <row r="38">
@@ -1445,11 +1445,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.6133209466934204</v>
+        <v>0.9891004681216021</v>
       </c>
     </row>
     <row r="39">
@@ -1472,11 +1472,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.5604366064071655</v>
+        <v>0.9891004681216021</v>
       </c>
     </row>
     <row r="40">
@@ -1499,11 +1499,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.4964616298675537</v>
+        <v>0.9891004681216021</v>
       </c>
     </row>
     <row r="41">
@@ -1526,11 +1526,11 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.5406022667884827</v>
+        <v>0.9891004681216021</v>
       </c>
     </row>
     <row r="42">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.3290696144104004</v>
+        <v>0.9891004681216021</v>
       </c>
     </row>
     <row r="43">
@@ -1580,11 +1580,11 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.4040665030479431</v>
+        <v>0.9891004681216021</v>
       </c>
     </row>
     <row r="44">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.374951183795929</v>
+        <v>0.9891004681216021</v>
       </c>
     </row>
     <row r="45">
@@ -1634,11 +1634,11 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.4085499048233032</v>
+        <v>0.9834838073724063</v>
       </c>
     </row>
     <row r="46">
@@ -1661,11 +1661,11 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.2875024676322937</v>
+        <v>0.9834838073724063</v>
       </c>
     </row>
     <row r="47">
@@ -1688,11 +1688,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.2658409476280212</v>
+        <v>0.9834838073724063</v>
       </c>
     </row>
     <row r="48">
@@ -1715,11 +1715,11 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.2679808437824249</v>
+        <v>0.9834838073724063</v>
       </c>
     </row>
     <row r="49">
@@ -1742,11 +1742,11 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.2766311764717102</v>
+        <v>0.9834838073724063</v>
       </c>
     </row>
     <row r="50">
@@ -1769,11 +1769,11 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.3400980234146118</v>
+        <v>0.9834838073724063</v>
       </c>
     </row>
     <row r="51">
@@ -1796,11 +1796,11 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.325573593378067</v>
+        <v>0.9834838073724063</v>
       </c>
     </row>
     <row r="52">
@@ -1823,11 +1823,11 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.2841066420078278</v>
+        <v>0.9834838073724063</v>
       </c>
     </row>
     <row r="53">
@@ -1850,11 +1850,11 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.4845289587974548</v>
+        <v>0.9604526415485182</v>
       </c>
     </row>
     <row r="54">
@@ -1877,11 +1877,11 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.6840542554855347</v>
+        <v>0.9604526415485182</v>
       </c>
     </row>
     <row r="55">
@@ -1904,11 +1904,11 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.7351782321929932</v>
+        <v>0.9604526415485182</v>
       </c>
     </row>
     <row r="56">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.6939308047294617</v>
+        <v>0.9604526415485182</v>
       </c>
     </row>
     <row r="57">
@@ -1958,11 +1958,11 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.6605193614959717</v>
+        <v>0.9604526415485182</v>
       </c>
     </row>
     <row r="58">
@@ -1985,11 +1985,11 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.6804382801055908</v>
+        <v>0.9604526415485182</v>
       </c>
     </row>
     <row r="59">
@@ -2012,11 +2012,11 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.7013087868690491</v>
+        <v>0.9604526415485182</v>
       </c>
     </row>
     <row r="60">
@@ -2039,11 +2039,11 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.6174338459968567</v>
+        <v>0.9604526415485182</v>
       </c>
     </row>
     <row r="61">
@@ -2066,11 +2066,11 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.61248379945755</v>
+        <v>0.9890341604929163</v>
       </c>
     </row>
     <row r="62">
@@ -2093,11 +2093,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.7407562732696533</v>
+        <v>0.9890341604929163</v>
       </c>
     </row>
     <row r="63">
@@ -2120,11 +2120,11 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.7390108704566956</v>
+        <v>0.9890341604929163</v>
       </c>
     </row>
     <row r="64">
@@ -2147,11 +2147,11 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.787247896194458</v>
+        <v>0.9890341604929163</v>
       </c>
     </row>
     <row r="65">
@@ -2174,11 +2174,11 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.7354289889335632</v>
+        <v>0.9890341604929163</v>
       </c>
     </row>
     <row r="66">
@@ -2201,11 +2201,11 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.8306148648262024</v>
+        <v>0.9890341604929163</v>
       </c>
     </row>
     <row r="67">
@@ -2228,11 +2228,11 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.7947258353233337</v>
+        <v>0.9890341604929163</v>
       </c>
     </row>
     <row r="68">
@@ -2255,11 +2255,11 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.7930605411529541</v>
+        <v>0.9890341604929163</v>
       </c>
     </row>
     <row r="69">
@@ -2282,11 +2282,11 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.807090699672699</v>
+        <v>0.9669047950774077</v>
       </c>
     </row>
     <row r="70">
@@ -2309,11 +2309,11 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.795238196849823</v>
+        <v>0.9669047950774077</v>
       </c>
     </row>
     <row r="71">
@@ -2336,11 +2336,11 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.7969403862953186</v>
+        <v>0.9669047950774077</v>
       </c>
     </row>
     <row r="72">
@@ -2363,11 +2363,11 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.8647505640983582</v>
+        <v>0.9669047950774077</v>
       </c>
     </row>
     <row r="73">
@@ -2390,11 +2390,11 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.7837191224098206</v>
+        <v>0.9669047950774077</v>
       </c>
     </row>
     <row r="74">
@@ -2417,11 +2417,11 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.7919773459434509</v>
+        <v>0.9669047950774077</v>
       </c>
     </row>
     <row r="75">
@@ -2444,11 +2444,11 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.875853419303894</v>
+        <v>0.9669047950774077</v>
       </c>
     </row>
     <row r="76">
@@ -2471,11 +2471,11 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.8802773356437683</v>
+        <v>0.9669047950774077</v>
       </c>
     </row>
     <row r="77">
@@ -2498,11 +2498,11 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.9157395362854004</v>
+        <v>0.9664495306799028</v>
       </c>
     </row>
     <row r="78">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.8129280805587769</v>
+        <v>0.9664495306799028</v>
       </c>
     </row>
     <row r="79">
@@ -2552,11 +2552,11 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.8212933540344238</v>
+        <v>0.9664495306799028</v>
       </c>
     </row>
     <row r="80">
@@ -2579,11 +2579,11 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.9074651598930359</v>
+        <v>0.9664495306799028</v>
       </c>
     </row>
     <row r="81">
@@ -2606,11 +2606,11 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.9456495046615601</v>
+        <v>0.9664495306799028</v>
       </c>
     </row>
     <row r="82">
@@ -2633,11 +2633,11 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.9701720476150513</v>
+        <v>0.9664495306799028</v>
       </c>
     </row>
     <row r="83">
@@ -2660,11 +2660,11 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.9714017510414124</v>
+        <v>0.9664495306799028</v>
       </c>
     </row>
     <row r="84">
@@ -2687,11 +2687,11 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.9688941240310669</v>
+        <v>0.9664495306799028</v>
       </c>
     </row>
     <row r="85">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.9371048212051392</v>
+        <v>0.962819632622044</v>
       </c>
     </row>
     <row r="86">
@@ -2741,11 +2741,11 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.9397813677787781</v>
+        <v>0.962819632622044</v>
       </c>
     </row>
     <row r="87">
@@ -2768,11 +2768,11 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.9069178104400635</v>
+        <v>0.962819632622044</v>
       </c>
     </row>
     <row r="88">
@@ -2795,11 +2795,11 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.863016664981842</v>
+        <v>0.962819632622044</v>
       </c>
     </row>
     <row r="89">
@@ -2822,11 +2822,11 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.9307433366775513</v>
+        <v>0.962819632622044</v>
       </c>
     </row>
     <row r="90">
@@ -2849,11 +2849,11 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.9459629058837891</v>
+        <v>0.962819632622044</v>
       </c>
     </row>
     <row r="91">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.863042414188385</v>
+        <v>0.962819632622044</v>
       </c>
     </row>
     <row r="92">
@@ -2903,11 +2903,11 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.8528290390968323</v>
+        <v>0.962819632622044</v>
       </c>
     </row>
     <row r="93">
@@ -2930,11 +2930,11 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.7478647232055664</v>
+        <v>0.9779511237995836</v>
       </c>
     </row>
     <row r="94">
@@ -2957,11 +2957,11 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.8238345384597778</v>
+        <v>0.9779511237995836</v>
       </c>
     </row>
     <row r="95">
@@ -2984,11 +2984,11 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.8182815909385681</v>
+        <v>0.9779511237995836</v>
       </c>
     </row>
     <row r="96">
@@ -3011,11 +3011,11 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.8510395884513855</v>
+        <v>0.9779511237995836</v>
       </c>
     </row>
     <row r="97">
@@ -3038,11 +3038,11 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.737769603729248</v>
+        <v>0.9779511237995836</v>
       </c>
     </row>
     <row r="98">
@@ -3065,11 +3065,11 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.5728322863578796</v>
+        <v>0.9779511237995836</v>
       </c>
     </row>
     <row r="99">
@@ -3092,11 +3092,11 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.5940243601799011</v>
+        <v>0.9779511237995836</v>
       </c>
     </row>
     <row r="100">
@@ -3119,11 +3119,11 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.635890781879425</v>
+        <v>0.9779511237995836</v>
       </c>
     </row>
     <row r="101">
@@ -3146,11 +3146,11 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.7070457339286804</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="102">
@@ -3173,11 +3173,11 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.6414940357208252</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="103">
@@ -3200,11 +3200,11 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="104">
@@ -3227,11 +3227,11 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="105">
@@ -3254,11 +3254,11 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="106">
@@ -3281,11 +3281,11 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="107">
@@ -3308,11 +3308,11 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="108">
@@ -3335,11 +3335,11 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="109">
@@ -3362,11 +3362,11 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="110">
@@ -3389,11 +3389,11 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="111">
@@ -3416,11 +3416,11 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="112">
@@ -3443,11 +3443,11 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="113">
@@ -3470,11 +3470,11 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="114">
@@ -3497,11 +3497,11 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="115">
@@ -3524,11 +3524,11 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="116">
@@ -3551,11 +3551,11 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="117">
@@ -3578,11 +3578,11 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="118">
@@ -3605,11 +3605,11 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="119">
@@ -3632,11 +3632,11 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="120">
@@ -3659,11 +3659,11 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.6199290156364441</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="121">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.722940981388092</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="122">
@@ -3713,11 +3713,11 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.8386943936347961</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="123">
@@ -3740,11 +3740,11 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.7756814956665039</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="124">
@@ -3767,11 +3767,11 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.6871659159660339</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="125">
@@ -3794,11 +3794,11 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.7189462780952454</v>
+        <v>0.9627461211419187</v>
       </c>
     </row>
     <row r="126">
@@ -3821,11 +3821,11 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.8275006413459778</v>
+        <v>0.9606145343937719</v>
       </c>
     </row>
     <row r="127">
@@ -3848,11 +3848,11 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.6053079962730408</v>
+        <v>0.9606145343937719</v>
       </c>
     </row>
     <row r="128">
@@ -3875,11 +3875,11 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.5819188952445984</v>
+        <v>0.9606145343937719</v>
       </c>
     </row>
     <row r="129">
@@ -3902,11 +3902,11 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.2861277759075165</v>
+        <v>0.9606145343937719</v>
       </c>
     </row>
     <row r="130">
@@ -3929,11 +3929,11 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.4364338517189026</v>
+        <v>0.9606145343937719</v>
       </c>
     </row>
     <row r="131">
@@ -3956,11 +3956,11 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.4528271853923798</v>
+        <v>0.9606145343937719</v>
       </c>
     </row>
     <row r="132">
@@ -3983,11 +3983,11 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.5496089458465576</v>
+        <v>0.9606145343937719</v>
       </c>
     </row>
     <row r="133">
@@ -4010,11 +4010,11 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.5664043426513672</v>
+        <v>0.9606145343937719</v>
       </c>
     </row>
     <row r="134">
@@ -4037,11 +4037,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.5999982357025146</v>
+        <v>0.9775281962207837</v>
       </c>
     </row>
     <row r="135">
@@ -4064,11 +4064,11 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.6536296606063843</v>
+        <v>0.9775281962207837</v>
       </c>
     </row>
     <row r="136">
@@ -4091,11 +4091,11 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.5385997295379639</v>
+        <v>0.9775281962207837</v>
       </c>
     </row>
     <row r="137">
@@ -4118,11 +4118,11 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.6197578907012939</v>
+        <v>0.9775281962207837</v>
       </c>
     </row>
     <row r="138">
@@ -4145,11 +4145,11 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.7713463306427002</v>
+        <v>0.9775281962207837</v>
       </c>
     </row>
     <row r="139">
@@ -4172,11 +4172,11 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.7667298913002014</v>
+        <v>0.9775281962207837</v>
       </c>
     </row>
     <row r="140">
@@ -4199,11 +4199,11 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.7684869170188904</v>
+        <v>0.9775281962207837</v>
       </c>
     </row>
     <row r="141">
@@ -4226,11 +4226,11 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.6411083340644836</v>
+        <v>0.9775281962207837</v>
       </c>
     </row>
     <row r="142">
@@ -4253,11 +4253,11 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.5936500430107117</v>
+        <v>0.9822390547374903</v>
       </c>
     </row>
     <row r="143">
@@ -4280,11 +4280,11 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.3150626420974731</v>
+        <v>0.9822390547374903</v>
       </c>
     </row>
     <row r="144">
@@ -4307,11 +4307,11 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.3630351126194</v>
+        <v>0.9822390547374903</v>
       </c>
     </row>
     <row r="145">
@@ -4334,11 +4334,11 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.3534648418426514</v>
+        <v>0.9822390547374903</v>
       </c>
     </row>
     <row r="146">
@@ -4361,11 +4361,11 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.371883362531662</v>
+        <v>0.9822390547374903</v>
       </c>
     </row>
     <row r="147">
@@ -4388,11 +4388,11 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.511097252368927</v>
+        <v>0.9822390547374903</v>
       </c>
     </row>
     <row r="148">
@@ -4415,11 +4415,11 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.3557369112968445</v>
+        <v>0.9822390547374903</v>
       </c>
     </row>
     <row r="149">
@@ -4442,11 +4442,11 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.3581353425979614</v>
+        <v>0.9822390547374903</v>
       </c>
     </row>
     <row r="150">
@@ -4469,11 +4469,11 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.2520619630813599</v>
+        <v>0.9660179940525567</v>
       </c>
     </row>
     <row r="151">
@@ -4496,11 +4496,11 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.1782819628715515</v>
+        <v>0.9660179940525567</v>
       </c>
     </row>
     <row r="152">
@@ -4523,11 +4523,11 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.2199521064758301</v>
+        <v>0.9660179940525567</v>
       </c>
     </row>
     <row r="153">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.1472478210926056</v>
+        <v>0.9660179940525567</v>
       </c>
     </row>
     <row r="154">
@@ -4577,11 +4577,11 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.1919280886650085</v>
+        <v>0.9660179940525567</v>
       </c>
     </row>
     <row r="155">
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.1927475035190582</v>
+        <v>0.9660179940525567</v>
       </c>
     </row>
     <row r="156">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Shooting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.161251425743103</v>
+        <v>0.9660179940525567</v>
       </c>
     </row>
     <row r="157">
@@ -4658,11 +4658,11 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.1714316159486771</v>
+        <v>0.9660179940525567</v>
       </c>
     </row>
     <row r="158">
@@ -4685,11 +4685,11 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.1877641379833221</v>
+        <v>0.9841008778917502</v>
       </c>
     </row>
     <row r="159">
@@ -4712,11 +4712,11 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.1972203403711319</v>
+        <v>0.9841008778917502</v>
       </c>
     </row>
     <row r="160">
@@ -4739,11 +4739,11 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.2846330106258392</v>
+        <v>0.9841008778917502</v>
       </c>
     </row>
     <row r="161">
@@ -4766,11 +4766,11 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.1677224338054657</v>
+        <v>0.9841008778917502</v>
       </c>
     </row>
     <row r="162">
@@ -4793,11 +4793,11 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.1789996773004532</v>
+        <v>0.9841008778917502</v>
       </c>
     </row>
     <row r="163">
@@ -4820,11 +4820,11 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.1732943505048752</v>
+        <v>0.9841008778917502</v>
       </c>
     </row>
     <row r="164">
@@ -4847,11 +4847,11 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.2241509705781937</v>
+        <v>0.9841008778917502</v>
       </c>
     </row>
     <row r="165">
@@ -4874,11 +4874,11 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.1111753284931183</v>
+        <v>0.9841008778917502</v>
       </c>
     </row>
     <row r="166">
@@ -4901,11 +4901,11 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.1410299837589264</v>
+        <v>0.9618227512155274</v>
       </c>
     </row>
     <row r="167">
@@ -4928,11 +4928,11 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.1288329660892487</v>
+        <v>0.9618227512155274</v>
       </c>
     </row>
     <row r="168">
@@ -4955,11 +4955,11 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.1459379643201828</v>
+        <v>0.9618227512155274</v>
       </c>
     </row>
     <row r="169">
@@ -4982,11 +4982,11 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.1829065531492233</v>
+        <v>0.9618227512155274</v>
       </c>
     </row>
     <row r="170">
@@ -5009,11 +5009,11 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.1912135481834412</v>
+        <v>0.9618227512155274</v>
       </c>
     </row>
     <row r="171">
@@ -5036,11 +5036,11 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.2451093643903732</v>
+        <v>0.9618227512155274</v>
       </c>
     </row>
     <row r="172">
@@ -5063,11 +5063,11 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.3878796100616455</v>
+        <v>0.9618227512155274</v>
       </c>
     </row>
     <row r="173">
@@ -5090,11 +5090,11 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.5312464833259583</v>
+        <v>0.9618227512155274</v>
       </c>
     </row>
     <row r="174">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.501325786113739</v>
+        <v>0.988083094147496</v>
       </c>
     </row>
     <row r="175">
@@ -5144,11 +5144,11 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.4660066366195679</v>
+        <v>0.988083094147496</v>
       </c>
     </row>
     <row r="176">
@@ -5171,11 +5171,11 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.3489885628223419</v>
+        <v>0.988083094147496</v>
       </c>
     </row>
     <row r="177">
@@ -5198,11 +5198,11 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.2693963944911957</v>
+        <v>0.988083094147496</v>
       </c>
     </row>
     <row r="178">
@@ -5225,11 +5225,11 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.23826864361763</v>
+        <v>0.988083094147496</v>
       </c>
     </row>
     <row r="179">
@@ -5252,11 +5252,11 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.2493911385536194</v>
+        <v>0.988083094147496</v>
       </c>
     </row>
     <row r="180">
@@ -5279,11 +5279,11 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.2555256187915802</v>
+        <v>0.988083094147496</v>
       </c>
     </row>
     <row r="181">
@@ -5306,11 +5306,11 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.2611398100852966</v>
+        <v>0.988083094147496</v>
       </c>
     </row>
     <row r="182">
@@ -5333,11 +5333,11 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.2195067405700684</v>
+        <v>0.9675743865277908</v>
       </c>
     </row>
     <row r="183">
@@ -5360,11 +5360,11 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.3111039996147156</v>
+        <v>0.9675743865277908</v>
       </c>
     </row>
     <row r="184">
@@ -5387,11 +5387,11 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.3224012851715088</v>
+        <v>0.9675743865277908</v>
       </c>
     </row>
     <row r="185">
@@ -5414,11 +5414,11 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.1574168801307678</v>
+        <v>0.9675743865277908</v>
       </c>
     </row>
     <row r="186">
@@ -5441,11 +5441,11 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.2043048143386841</v>
+        <v>0.9675743865277908</v>
       </c>
     </row>
     <row r="187">
@@ -5468,11 +5468,11 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.185088649392128</v>
+        <v>0.9675743865277908</v>
       </c>
     </row>
     <row r="188">
@@ -5495,11 +5495,11 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.20931676030159</v>
+        <v>0.9675743865277908</v>
       </c>
     </row>
     <row r="189">
@@ -5522,11 +5522,11 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.1565872877836227</v>
+        <v>0.9675743865277908</v>
       </c>
     </row>
     <row r="190">
@@ -5549,11 +5549,11 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.1493858098983765</v>
+        <v>0.9839026985807184</v>
       </c>
     </row>
     <row r="191">
@@ -5576,11 +5576,11 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.1969349682331085</v>
+        <v>0.9839026985807184</v>
       </c>
     </row>
     <row r="192">
@@ -5603,11 +5603,11 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.1682041138410568</v>
+        <v>0.9839026985807184</v>
       </c>
     </row>
     <row r="193">
@@ -5630,11 +5630,11 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.1946844756603241</v>
+        <v>0.9839026985807184</v>
       </c>
     </row>
     <row r="194">
@@ -5657,11 +5657,11 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.2366293221712112</v>
+        <v>0.9839026985807184</v>
       </c>
     </row>
     <row r="195">
@@ -5684,11 +5684,11 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.2763941287994385</v>
+        <v>0.9839026985807184</v>
       </c>
     </row>
     <row r="196">
@@ -5711,11 +5711,11 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.2015767842531204</v>
+        <v>0.9839026985807184</v>
       </c>
     </row>
     <row r="197">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.3448265492916107</v>
+        <v>0.9839026985807184</v>
       </c>
     </row>
     <row r="198">
@@ -5765,11 +5765,11 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.3843050003051758</v>
+        <v>0.9660241400454463</v>
       </c>
     </row>
     <row r="199">
@@ -5792,11 +5792,11 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.4702809751033783</v>
+        <v>0.9660241400454463</v>
       </c>
     </row>
     <row r="200">
@@ -5819,11 +5819,11 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.505136251449585</v>
+        <v>0.9660241400454463</v>
       </c>
     </row>
     <row r="201">
@@ -5846,11 +5846,11 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.451396107673645</v>
+        <v>0.9660241400454463</v>
       </c>
     </row>
     <row r="202">
@@ -5873,11 +5873,11 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.5735556483268738</v>
+        <v>0.9660241400454463</v>
       </c>
     </row>
     <row r="203">
@@ -5900,11 +5900,11 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.5732821822166443</v>
+        <v>0.9660241400454463</v>
       </c>
     </row>
     <row r="204">
@@ -5927,11 +5927,11 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.3546359539031982</v>
+        <v>0.9660241400454463</v>
       </c>
     </row>
     <row r="205">
@@ -5954,11 +5954,11 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.2223792374134064</v>
+        <v>0.9660241400454463</v>
       </c>
     </row>
     <row r="206">
@@ -5981,11 +5981,11 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.2518367171287537</v>
+        <v>0.9708959849167033</v>
       </c>
     </row>
     <row r="207">
@@ -6008,11 +6008,11 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.300858199596405</v>
+        <v>0.9708959849167033</v>
       </c>
     </row>
     <row r="208">
@@ -6035,11 +6035,11 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.2731035053730011</v>
+        <v>0.9708959849167033</v>
       </c>
     </row>
     <row r="209">
@@ -6062,11 +6062,11 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.3373992741107941</v>
+        <v>0.9708959849167033</v>
       </c>
     </row>
     <row r="210">
@@ -6089,11 +6089,11 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.3075236082077026</v>
+        <v>0.9708959849167033</v>
       </c>
     </row>
     <row r="211">
@@ -6116,11 +6116,11 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.3469946682453156</v>
+        <v>0.9708959849167033</v>
       </c>
     </row>
     <row r="212">
@@ -6143,11 +6143,11 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.4008961319923401</v>
+        <v>0.9708959849167033</v>
       </c>
     </row>
     <row r="213">
@@ -6170,11 +6170,11 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.3270218968391418</v>
+        <v>0.9708959849167033</v>
       </c>
     </row>
     <row r="214">
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.239373967051506</v>
+        <v>0.9800723183744335</v>
       </c>
     </row>
     <row r="215">
@@ -6224,11 +6224,11 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.219246119260788</v>
+        <v>0.9800723183744335</v>
       </c>
     </row>
     <row r="216">
@@ -6251,11 +6251,11 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.1895845383405685</v>
+        <v>0.9800723183744335</v>
       </c>
     </row>
     <row r="217">
@@ -6278,11 +6278,11 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.3214421570301056</v>
+        <v>0.9800723183744335</v>
       </c>
     </row>
     <row r="218">
@@ -6305,11 +6305,11 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.4249551892280579</v>
+        <v>0.9800723183744335</v>
       </c>
     </row>
     <row r="219">
@@ -6332,11 +6332,11 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.5161861777305603</v>
+        <v>0.9800723183744335</v>
       </c>
     </row>
     <row r="220">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.678965151309967</v>
+        <v>0.9800723183744335</v>
       </c>
     </row>
     <row r="221">
@@ -6386,11 +6386,11 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.7083490490913391</v>
+        <v>0.9800723183744335</v>
       </c>
     </row>
     <row r="222">
@@ -6413,11 +6413,11 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.6448051929473877</v>
+        <v>0.9892742802040492</v>
       </c>
     </row>
     <row r="223">
@@ -6440,11 +6440,11 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.5196262001991272</v>
+        <v>0.9892742802040492</v>
       </c>
     </row>
     <row r="224">
@@ -6467,11 +6467,11 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.4563276767730713</v>
+        <v>0.9892742802040492</v>
       </c>
     </row>
     <row r="225">
@@ -6494,11 +6494,11 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.4293237924575806</v>
+        <v>0.9892742802040492</v>
       </c>
     </row>
     <row r="226">
@@ -6521,11 +6521,11 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.3807041049003601</v>
+        <v>0.9892742802040492</v>
       </c>
     </row>
     <row r="227">
@@ -6548,11 +6548,11 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.3824127316474915</v>
+        <v>0.9892742802040492</v>
       </c>
     </row>
     <row r="228">
@@ -6575,11 +6575,11 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.3459051549434662</v>
+        <v>0.9892742802040492</v>
       </c>
     </row>
     <row r="229">
@@ -6602,11 +6602,11 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.3759344518184662</v>
+        <v>0.9892742802040492</v>
       </c>
     </row>
     <row r="230">
@@ -6629,11 +6629,11 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.4579927921295166</v>
+        <v>0.9682440699362301</v>
       </c>
     </row>
     <row r="231">
@@ -6656,11 +6656,11 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.4141584038734436</v>
+        <v>0.9682440699362301</v>
       </c>
     </row>
     <row r="232">
@@ -6683,11 +6683,11 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.2322037816047668</v>
+        <v>0.9682440699362301</v>
       </c>
     </row>
     <row r="233">
@@ -6710,11 +6710,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.2398458123207092</v>
+        <v>0.9682440699362301</v>
       </c>
     </row>
     <row r="234">
@@ -6737,11 +6737,11 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.1733560562133789</v>
+        <v>0.9682440699362301</v>
       </c>
     </row>
     <row r="235">
@@ -6764,11 +6764,11 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.2912017107009888</v>
+        <v>0.9682440699362301</v>
       </c>
     </row>
     <row r="236">
@@ -6791,11 +6791,11 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.3488552570343018</v>
+        <v>0.9682440699362301</v>
       </c>
     </row>
     <row r="237">
@@ -6818,11 +6818,11 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.4104827046394348</v>
+        <v>0.9682440699362301</v>
       </c>
     </row>
     <row r="238">
@@ -6845,11 +6845,11 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.5101513862609863</v>
+        <v>0.9766816183443392</v>
       </c>
     </row>
     <row r="239">
@@ -6872,11 +6872,11 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.6294840574264526</v>
+        <v>0.9766816183443392</v>
       </c>
     </row>
     <row r="240">
@@ -6899,11 +6899,11 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.6207448244094849</v>
+        <v>0.9766816183443392</v>
       </c>
     </row>
     <row r="241">
@@ -6926,11 +6926,11 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.5360221862792969</v>
+        <v>0.9766816183443392</v>
       </c>
     </row>
     <row r="242">
@@ -6953,11 +6953,11 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.4642940163612366</v>
+        <v>0.9766816183443392</v>
       </c>
     </row>
     <row r="243">
@@ -6980,11 +6980,11 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.4334756135940552</v>
+        <v>0.9766816183443392</v>
       </c>
     </row>
     <row r="244">
@@ -7007,11 +7007,11 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.3660476803779602</v>
+        <v>0.9766816183443392</v>
       </c>
     </row>
     <row r="245">
@@ -7034,11 +7034,11 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.4979607462882996</v>
+        <v>0.9766816183443392</v>
       </c>
     </row>
     <row r="246">
@@ -7061,11 +7061,11 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.6884436011314392</v>
+        <v>0.9833577953194771</v>
       </c>
     </row>
     <row r="247">
@@ -7088,11 +7088,11 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.6473532915115356</v>
+        <v>0.9833577953194771</v>
       </c>
     </row>
     <row r="248">
@@ -7115,11 +7115,11 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.4560596942901611</v>
+        <v>0.9833577953194771</v>
       </c>
     </row>
     <row r="249">
@@ -7142,11 +7142,11 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.4782726168632507</v>
+        <v>0.9833577953194771</v>
       </c>
     </row>
     <row r="250">
@@ -7169,11 +7169,11 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.5025320649147034</v>
+        <v>0.9833577953194771</v>
       </c>
     </row>
     <row r="251">
@@ -7196,11 +7196,11 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.508134126663208</v>
+        <v>0.9833577953194771</v>
       </c>
     </row>
     <row r="252">
@@ -7223,11 +7223,11 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.4806845188140869</v>
+        <v>0.9833577953194771</v>
       </c>
     </row>
     <row r="253">
@@ -7250,11 +7250,11 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.402041494846344</v>
+        <v>0.9833577953194771</v>
       </c>
     </row>
     <row r="254">
@@ -7277,11 +7277,11 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.4011599719524384</v>
+        <v>0.9647152900875987</v>
       </c>
     </row>
     <row r="255">
@@ -7304,11 +7304,11 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.3896733224391937</v>
+        <v>0.9647152900875987</v>
       </c>
     </row>
     <row r="256">
@@ -7331,11 +7331,11 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.2870203256607056</v>
+        <v>0.9647152900875987</v>
       </c>
     </row>
     <row r="257">
@@ -7358,11 +7358,11 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.3215683996677399</v>
+        <v>0.9647152900875987</v>
       </c>
     </row>
     <row r="258">
@@ -7385,11 +7385,11 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.3018307983875275</v>
+        <v>0.9647152900875987</v>
       </c>
     </row>
     <row r="259">
@@ -7412,11 +7412,11 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.3746731877326965</v>
+        <v>0.9647152900875987</v>
       </c>
     </row>
     <row r="260">
@@ -7439,11 +7439,11 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.4415083229541779</v>
+        <v>0.9647152900875987</v>
       </c>
     </row>
     <row r="261">
@@ -7466,11 +7466,11 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.3855180442333221</v>
+        <v>0.9647152900875987</v>
       </c>
     </row>
     <row r="262">
@@ -7493,11 +7493,11 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.2663815915584564</v>
+        <v>0.9613771336900518</v>
       </c>
     </row>
     <row r="263">
@@ -7520,11 +7520,11 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Shooting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.2905373573303223</v>
+        <v>0.9613771336900518</v>
       </c>
     </row>
     <row r="264">
@@ -7547,11 +7547,11 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Shooting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.3109177350997925</v>
+        <v>0.9613771336900518</v>
       </c>
     </row>
     <row r="265">
@@ -7574,11 +7574,11 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Shooting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.4875672459602356</v>
+        <v>0.9613771336900518</v>
       </c>
     </row>
     <row r="266">
@@ -7601,11 +7601,11 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Shooting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.6139291524887085</v>
+        <v>0.9613771336900518</v>
       </c>
     </row>
     <row r="267">
@@ -7628,11 +7628,11 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Shooting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.6595316529273987</v>
+        <v>0.9613771336900518</v>
       </c>
     </row>
     <row r="268">
@@ -7655,11 +7655,11 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Shooting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.6009265184402466</v>
+        <v>0.9613771336900518</v>
       </c>
     </row>
     <row r="269">
@@ -7682,11 +7682,11 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Shooting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.4899857044219971</v>
+        <v>0.9613771336900518</v>
       </c>
     </row>
     <row r="270">
@@ -7709,11 +7709,11 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Shooting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.249241903424263</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="271">
@@ -7736,11 +7736,11 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="272">
@@ -7763,11 +7763,11 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="273">
@@ -7790,11 +7790,11 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="274">
@@ -7817,11 +7817,11 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="275">
@@ -7844,11 +7844,11 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="276">
@@ -7871,11 +7871,11 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="277">
@@ -7898,11 +7898,11 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="278">
@@ -7925,11 +7925,11 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="279">
@@ -7952,11 +7952,11 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="280">
@@ -7979,11 +7979,11 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="281">
@@ -8006,11 +8006,11 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="282">
@@ -8033,11 +8033,11 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="283">
@@ -8060,11 +8060,11 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="284">
@@ -8087,11 +8087,11 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="285">
@@ -8114,11 +8114,11 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.2117969989776611</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="286">
@@ -8141,11 +8141,11 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.3305812180042267</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="287">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.3305812180042267</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="288">
@@ -8195,11 +8195,11 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.3305812180042267</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="289">
@@ -8222,11 +8222,11 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="290">
@@ -8249,11 +8249,11 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="291">
@@ -8276,11 +8276,11 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="292">
@@ -8303,11 +8303,11 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="293">
@@ -8330,11 +8330,11 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="294">
@@ -8357,11 +8357,11 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="295">
@@ -8384,11 +8384,11 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="296">
@@ -8411,11 +8411,11 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="297">
@@ -8438,11 +8438,11 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="298">
@@ -8465,11 +8465,11 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="299">
@@ -8492,11 +8492,11 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="300">
@@ -8519,11 +8519,11 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="301">
@@ -8546,11 +8546,11 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="302">
@@ -8573,11 +8573,11 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G302" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="303">
@@ -8600,11 +8600,11 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="304">
@@ -8627,11 +8627,11 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G304" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="305">
@@ -8654,11 +8654,11 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="306">
@@ -8681,11 +8681,11 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G306" t="n">
-        <v>0.482107400894165</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="307">
@@ -8708,11 +8708,11 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G307" t="n">
-        <v>0.4338657557964325</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="308">
@@ -8735,11 +8735,11 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>0.4514027535915375</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="309">
@@ -8762,11 +8762,11 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>0.4344973266124725</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="310">
@@ -8789,11 +8789,11 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>0.5257815718650818</v>
+        <v>0.9641001895687177</v>
       </c>
     </row>
     <row r="311">
@@ -8816,11 +8816,11 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>0.4271192848682404</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="312">
@@ -8843,11 +8843,11 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>0.4271192848682404</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="313">
@@ -8870,11 +8870,11 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>0.4271192848682404</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="314">
@@ -8897,11 +8897,11 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>0.4271192848682404</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="315">
@@ -8924,11 +8924,11 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>0.5455682873725891</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="316">
@@ -8951,11 +8951,11 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>0.5455682873725891</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="317">
@@ -8978,11 +8978,11 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>0.5455682873725891</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="318">
@@ -9005,11 +9005,11 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>0.5455682873725891</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="319">
@@ -9032,11 +9032,11 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>0.5455682873725891</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="320">
@@ -9059,11 +9059,11 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>0.6362622976303101</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="321">
@@ -9086,11 +9086,11 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>0.5341617465019226</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="322">
@@ -9113,11 +9113,11 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>0.5342602729797363</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="323">
@@ -9140,11 +9140,11 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>0.5342602729797363</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="324">
@@ -9167,11 +9167,11 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>0.5342602729797363</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="325">
@@ -9194,11 +9194,11 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="326">
@@ -9221,11 +9221,11 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="327">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="328">
@@ -9275,11 +9275,11 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="329">
@@ -9302,11 +9302,11 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G329" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="330">
@@ -9329,11 +9329,11 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G330" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="331">
@@ -9356,11 +9356,11 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="332">
@@ -9383,11 +9383,11 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="333">
@@ -9410,11 +9410,11 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="334">
@@ -9437,11 +9437,11 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="335">
@@ -9464,11 +9464,11 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="336">
@@ -9491,11 +9491,11 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="337">
@@ -9518,11 +9518,11 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G337" t="n">
-        <v>0.6732222437858582</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="338">
@@ -9545,11 +9545,11 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>0.3899935781955719</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="339">
@@ -9572,11 +9572,11 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G339" t="n">
-        <v>0.3993136584758759</v>
+        <v>0.97148333180482</v>
       </c>
     </row>
     <row r="340">
@@ -9599,11 +9599,11 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>0.2824703454971313</v>
+        <v>0.6148138344287872</v>
       </c>
     </row>
     <row r="341">
@@ -9626,11 +9626,11 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>0.6269076466560364</v>
+        <v>0.6148138344287872</v>
       </c>
     </row>
     <row r="342">
@@ -9653,11 +9653,11 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>0.3827551901340485</v>
+        <v>0.6148138344287872</v>
       </c>
     </row>
     <row r="343">
@@ -9680,11 +9680,11 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>0.4023820459842682</v>
+        <v>0.6148138344287872</v>
       </c>
     </row>
     <row r="344">
@@ -9707,11 +9707,11 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>0.4594496488571167</v>
+        <v>0.6148138344287872</v>
       </c>
     </row>
     <row r="345">
@@ -9734,11 +9734,11 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>0.490231841802597</v>
+        <v>0.6148138344287872</v>
       </c>
     </row>
     <row r="346">
@@ -9761,11 +9761,11 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>0.4830011129379272</v>
+        <v>0.6148138344287872</v>
       </c>
     </row>
     <row r="347">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>0.487121045589447</v>
+        <v>0.6148138344287872</v>
       </c>
     </row>
     <row r="348">
@@ -9815,11 +9815,11 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>0.3988120555877686</v>
+        <v>0.3627716302871704</v>
       </c>
     </row>
     <row r="349">
@@ -9842,11 +9842,11 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>0.3661185503005981</v>
+        <v>0.3627716302871704</v>
       </c>
     </row>
     <row r="350">
@@ -9869,11 +9869,11 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G350" t="n">
-        <v>0.4185356199741364</v>
+        <v>0.3627716302871704</v>
       </c>
     </row>
     <row r="351">
@@ -9896,11 +9896,11 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G351" t="n">
-        <v>0.2897565960884094</v>
+        <v>0.3627716302871704</v>
       </c>
     </row>
     <row r="352">
@@ -9923,11 +9923,11 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G352" t="n">
-        <v>0.3204613924026489</v>
+        <v>0.3627716302871704</v>
       </c>
     </row>
     <row r="353">
@@ -9950,11 +9950,11 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G353" t="n">
-        <v>0.3194087743759155</v>
+        <v>0.3627716302871704</v>
       </c>
     </row>
     <row r="354">
@@ -9977,11 +9977,11 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G354" t="n">
-        <v>0.3045337200164795</v>
+        <v>0.3627716302871704</v>
       </c>
     </row>
     <row r="355">
@@ -10004,11 +10004,11 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>0.2264422625303268</v>
+        <v>0.3627716302871704</v>
       </c>
     </row>
     <row r="356">
@@ -10031,11 +10031,11 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>0.2755915820598602</v>
+        <v>0.9771435675215361</v>
       </c>
     </row>
     <row r="357">
@@ -10058,11 +10058,11 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G357" t="n">
-        <v>0.3484756648540497</v>
+        <v>0.9771435675215361</v>
       </c>
     </row>
     <row r="358">
@@ -10085,11 +10085,11 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G358" t="n">
-        <v>0.3752125203609467</v>
+        <v>0.9771435675215361</v>
       </c>
     </row>
     <row r="359">
@@ -10112,11 +10112,11 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0.2684293687343597</v>
+        <v>0.9771435675215361</v>
       </c>
     </row>
     <row r="360">
@@ -10139,11 +10139,11 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G360" t="n">
-        <v>0.3114399313926697</v>
+        <v>0.9771435675215361</v>
       </c>
     </row>
     <row r="361">
@@ -10166,11 +10166,11 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0.2833633124828339</v>
+        <v>0.9771435675215361</v>
       </c>
     </row>
     <row r="362">
@@ -10193,11 +10193,11 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>0.3393220901489258</v>
+        <v>0.9771435675215361</v>
       </c>
     </row>
     <row r="363">
@@ -10220,11 +10220,11 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>0.4030747413635254</v>
+        <v>0.9771435675215361</v>
       </c>
     </row>
     <row r="364">
@@ -10247,11 +10247,11 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>0.4956463277339935</v>
+        <v>0.9707946516095898</v>
       </c>
     </row>
     <row r="365">
@@ -10274,11 +10274,11 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>0.2963672578334808</v>
+        <v>0.9707946516095898</v>
       </c>
     </row>
     <row r="366">
@@ -10301,11 +10301,11 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>0.268552839756012</v>
+        <v>0.9707946516095898</v>
       </c>
     </row>
     <row r="367">
@@ -10328,11 +10328,11 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G367" t="n">
-        <v>0.2526883780956268</v>
+        <v>0.9707946516095898</v>
       </c>
     </row>
     <row r="368">
@@ -10355,11 +10355,11 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G368" t="n">
-        <v>0.2708227336406708</v>
+        <v>0.9707946516095898</v>
       </c>
     </row>
     <row r="369">
@@ -10382,11 +10382,11 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G369" t="n">
-        <v>0.2505489885807037</v>
+        <v>0.9707946516095898</v>
       </c>
     </row>
     <row r="370">
@@ -10409,11 +10409,11 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G370" t="n">
-        <v>0.2503783404827118</v>
+        <v>0.9707946516095898</v>
       </c>
     </row>
     <row r="371">
@@ -10436,11 +10436,11 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G371" t="n">
-        <v>0.2336250394582748</v>
+        <v>0.9707946516095898</v>
       </c>
     </row>
     <row r="372">
@@ -10463,11 +10463,11 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G372" t="n">
-        <v>0.4261378645896912</v>
+        <v>0.98362344724885</v>
       </c>
     </row>
     <row r="373">
@@ -10490,11 +10490,11 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G373" t="n">
-        <v>0.3039366006851196</v>
+        <v>0.98362344724885</v>
       </c>
     </row>
     <row r="374">
@@ -10517,11 +10517,11 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G374" t="n">
-        <v>0.3680679202079773</v>
+        <v>0.98362344724885</v>
       </c>
     </row>
     <row r="375">
@@ -10544,11 +10544,11 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G375" t="n">
-        <v>0.4608843624591827</v>
+        <v>0.98362344724885</v>
       </c>
     </row>
     <row r="376">
@@ -10571,11 +10571,11 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G376" t="n">
-        <v>0.7021750807762146</v>
+        <v>0.98362344724885</v>
       </c>
     </row>
     <row r="377">
@@ -10598,11 +10598,11 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G377" t="n">
-        <v>0.3602560758590698</v>
+        <v>0.98362344724885</v>
       </c>
     </row>
     <row r="378">
@@ -10625,11 +10625,11 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>0.2216776162385941</v>
+        <v>0.98362344724885</v>
       </c>
     </row>
     <row r="379">
@@ -10652,11 +10652,11 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>0.2426198422908783</v>
+        <v>0.98362344724885</v>
       </c>
     </row>
     <row r="380">
@@ -10679,11 +10679,11 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>0.4137155115604401</v>
+        <v>0.9881933164356246</v>
       </c>
     </row>
     <row r="381">
@@ -10706,11 +10706,11 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>0.7346704006195068</v>
+        <v>0.9881933164356246</v>
       </c>
     </row>
     <row r="382">
@@ -10733,11 +10733,11 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G382" t="n">
-        <v>0.4300397038459778</v>
+        <v>0.9881933164356246</v>
       </c>
     </row>
     <row r="383">
@@ -10760,11 +10760,11 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G383" t="n">
-        <v>0.5267831087112427</v>
+        <v>0.9881933164356246</v>
       </c>
     </row>
     <row r="384">
@@ -10787,11 +10787,11 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G384" t="n">
-        <v>0.3784196972846985</v>
+        <v>0.9881933164356246</v>
       </c>
     </row>
     <row r="385">
@@ -10814,11 +10814,11 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G385" t="n">
-        <v>0.4102258384227753</v>
+        <v>0.9881933164356246</v>
       </c>
     </row>
     <row r="386">
@@ -10841,11 +10841,11 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G386" t="n">
-        <v>0.3807168006896973</v>
+        <v>0.9881933164356246</v>
       </c>
     </row>
     <row r="387">
@@ -10868,11 +10868,11 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G387" t="n">
-        <v>0.4541183114051819</v>
+        <v>0.9881933164356246</v>
       </c>
     </row>
     <row r="388">
@@ -10895,11 +10895,11 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G388" t="n">
-        <v>0.4939006268978119</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="389">
@@ -10922,11 +10922,11 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G389" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="390">
@@ -10949,11 +10949,11 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G390" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="391">
@@ -10976,11 +10976,11 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G391" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="392">
@@ -11003,11 +11003,11 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G392" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="393">
@@ -11030,11 +11030,11 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G393" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="394">
@@ -11057,11 +11057,11 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G394" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="395">
@@ -11084,11 +11084,11 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G395" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="396">
@@ -11111,11 +11111,11 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G396" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="397">
@@ -11138,11 +11138,11 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G397" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="398">
@@ -11165,11 +11165,11 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G398" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="399">
@@ -11192,11 +11192,11 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G399" t="n">
-        <v>0.469731867313385</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="400">
@@ -11219,11 +11219,11 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G400" t="n">
-        <v>0.2815353870391846</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="401">
@@ -11246,11 +11246,11 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G401" t="n">
-        <v>0.5145915746688843</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="402">
@@ -11273,11 +11273,11 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G402" t="n">
-        <v>0.5993396043777466</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="403">
@@ -11300,11 +11300,11 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G403" t="n">
-        <v>0.6373492479324341</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="404">
@@ -11327,11 +11327,11 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G404" t="n">
-        <v>0.6723743081092834</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="405">
@@ -11354,11 +11354,11 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G405" t="n">
-        <v>0.6064894199371338</v>
+        <v>0.9851770677472589</v>
       </c>
     </row>
     <row r="406">
@@ -11381,11 +11381,11 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G406" t="n">
-        <v>0.3919407725334167</v>
+        <v>0.6866804957389832</v>
       </c>
     </row>
     <row r="407">
@@ -11408,11 +11408,11 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G407" t="n">
-        <v>0.4041106402873993</v>
+        <v>0.6866804957389832</v>
       </c>
     </row>
     <row r="408">
@@ -11435,11 +11435,11 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G408" t="n">
-        <v>0.4329345226287842</v>
+        <v>0.6866804957389832</v>
       </c>
     </row>
     <row r="409">
@@ -11462,11 +11462,11 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>0.4176444411277771</v>
+        <v>0.6866804957389832</v>
       </c>
     </row>
     <row r="410">
@@ -11489,11 +11489,11 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>0.5243667960166931</v>
+        <v>0.6866804957389832</v>
       </c>
     </row>
     <row r="411">
@@ -11516,11 +11516,11 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>0.3411168158054352</v>
+        <v>0.6866804957389832</v>
       </c>
     </row>
     <row r="412">
@@ -11543,11 +11543,11 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>0.4115976095199585</v>
+        <v>0.6866804957389832</v>
       </c>
     </row>
     <row r="413">
@@ -11570,11 +11570,11 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>0.3986246287822723</v>
+        <v>0.6866804957389832</v>
       </c>
     </row>
     <row r="414">
@@ -11597,11 +11597,11 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>0.4899973273277283</v>
+        <v>0.9033041596412659</v>
       </c>
     </row>
     <row r="415">
@@ -11624,11 +11624,11 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>0.4579049050807953</v>
+        <v>0.9033041596412659</v>
       </c>
     </row>
     <row r="416">
@@ -11651,11 +11651,11 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>0.4622552990913391</v>
+        <v>0.9033041596412659</v>
       </c>
     </row>
     <row r="417">
@@ -11678,11 +11678,11 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G417" t="n">
-        <v>0.4909403920173645</v>
+        <v>0.9033041596412659</v>
       </c>
     </row>
     <row r="418">
@@ -11705,11 +11705,11 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>0.3763660788536072</v>
+        <v>0.9033041596412659</v>
       </c>
     </row>
     <row r="419">
@@ -11732,11 +11732,11 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G419" t="n">
-        <v>0.4091350138187408</v>
+        <v>0.9033041596412659</v>
       </c>
     </row>
     <row r="420">
@@ -11759,11 +11759,11 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G420" t="n">
-        <v>0.3860003352165222</v>
+        <v>0.9033041596412659</v>
       </c>
     </row>
     <row r="421">
@@ -11786,11 +11786,11 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G421" t="n">
-        <v>0.4250497221946716</v>
+        <v>0.9033041596412659</v>
       </c>
     </row>
     <row r="422">
@@ -11813,11 +11813,11 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G422" t="n">
-        <v>0.3926169276237488</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="423">
@@ -11840,11 +11840,11 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G423" t="n">
-        <v>0.4955856502056122</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="424">
@@ -11867,11 +11867,11 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G424" t="n">
-        <v>0.4910554587841034</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="425">
@@ -11894,11 +11894,11 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G425" t="n">
-        <v>0.4030269980430603</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="426">
@@ -11921,11 +11921,11 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G426" t="n">
-        <v>0.4145922660827637</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="427">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G427" t="n">
-        <v>0.5664538741111755</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="428">
@@ -11975,11 +11975,11 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G428" t="n">
-        <v>0.5639376640319824</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="429">
@@ -12002,11 +12002,11 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G429" t="n">
-        <v>0.5399963855743408</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="430">
@@ -12029,11 +12029,11 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G430" t="n">
-        <v>0.5399963855743408</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="431">
@@ -12056,11 +12056,11 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G431" t="n">
-        <v>0.5399963855743408</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="432">
@@ -12083,11 +12083,11 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G432" t="n">
-        <v>0.5399963855743408</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="433">
@@ -12110,11 +12110,11 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G433" t="n">
-        <v>0.5399963855743408</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="434">
@@ -12137,11 +12137,11 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G434" t="n">
-        <v>0.5399963855743408</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="435">
@@ -12164,11 +12164,11 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G435" t="n">
-        <v>0.5399963855743408</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="436">
@@ -12191,11 +12191,11 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G436" t="n">
-        <v>0.5399963855743408</v>
+        <v>0.9694769546306644</v>
       </c>
     </row>
     <row r="437">
@@ -12218,11 +12218,11 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G437" t="n">
-        <v>0.542186439037323</v>
+        <v>0.7199372053146362</v>
       </c>
     </row>
     <row r="438">
@@ -12245,11 +12245,11 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G438" t="n">
-        <v>0.7247616648674011</v>
+        <v>0.7199372053146362</v>
       </c>
     </row>
     <row r="439">
@@ -12272,11 +12272,11 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G439" t="n">
-        <v>0.3684684932231903</v>
+        <v>0.7199372053146362</v>
       </c>
     </row>
     <row r="440">
@@ -12299,11 +12299,11 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G440" t="n">
-        <v>0.3192338347434998</v>
+        <v>0.7199372053146362</v>
       </c>
     </row>
     <row r="441">
@@ -12326,11 +12326,11 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G441" t="n">
-        <v>0.2966431677341461</v>
+        <v>0.7199372053146362</v>
       </c>
     </row>
     <row r="442">
@@ -12353,11 +12353,11 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G442" t="n">
-        <v>0.360272228717804</v>
+        <v>0.7199372053146362</v>
       </c>
     </row>
     <row r="443">
@@ -12380,11 +12380,11 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G443" t="n">
-        <v>0.4288017451763153</v>
+        <v>0.7199372053146362</v>
       </c>
     </row>
     <row r="444">
@@ -12407,11 +12407,11 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G444" t="n">
-        <v>0.512143611907959</v>
+        <v>0.7199372053146362</v>
       </c>
     </row>
     <row r="445">
@@ -12434,11 +12434,11 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G445" t="n">
-        <v>0.4752775132656097</v>
+        <v>0.880293145775795</v>
       </c>
     </row>
     <row r="446">
@@ -12461,11 +12461,11 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G446" t="n">
-        <v>0.4906625747680664</v>
+        <v>0.880293145775795</v>
       </c>
     </row>
     <row r="447">
@@ -12488,11 +12488,11 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G447" t="n">
-        <v>0.6164500713348389</v>
+        <v>0.880293145775795</v>
       </c>
     </row>
     <row r="448">
@@ -12515,11 +12515,11 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G448" t="n">
-        <v>0.482072114944458</v>
+        <v>0.880293145775795</v>
       </c>
     </row>
     <row r="449">
@@ -12542,11 +12542,11 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G449" t="n">
-        <v>0.4403696656227112</v>
+        <v>0.880293145775795</v>
       </c>
     </row>
     <row r="450">
@@ -12569,11 +12569,11 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G450" t="n">
-        <v>0.3202277421951294</v>
+        <v>0.880293145775795</v>
       </c>
     </row>
     <row r="451">
@@ -12596,11 +12596,11 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>0.3320751190185547</v>
+        <v>0.880293145775795</v>
       </c>
     </row>
     <row r="452">
@@ -12623,11 +12623,11 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G452" t="n">
-        <v>0.4416286945343018</v>
+        <v>0.880293145775795</v>
       </c>
     </row>
     <row r="453">
@@ -12650,11 +12650,11 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>0.6491219997406006</v>
+        <v>0.6803564429283142</v>
       </c>
     </row>
     <row r="454">
@@ -12677,11 +12677,11 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G454" t="n">
-        <v>0.8259477019309998</v>
+        <v>0.6803564429283142</v>
       </c>
     </row>
     <row r="455">
@@ -12704,11 +12704,11 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>0.8342925310134888</v>
+        <v>0.6803564429283142</v>
       </c>
     </row>
     <row r="456">
@@ -12731,11 +12731,11 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G456" t="n">
-        <v>0.8499767780303955</v>
+        <v>0.6803564429283142</v>
       </c>
     </row>
     <row r="457">
@@ -12758,11 +12758,11 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G457" t="n">
-        <v>0.6855142712593079</v>
+        <v>0.6803564429283142</v>
       </c>
     </row>
     <row r="458">
@@ -12785,11 +12785,11 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G458" t="n">
-        <v>0.6446556448936462</v>
+        <v>0.6803564429283142</v>
       </c>
     </row>
     <row r="459">
@@ -12812,11 +12812,11 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G459" t="n">
-        <v>0.578496515750885</v>
+        <v>0.6803564429283142</v>
       </c>
     </row>
     <row r="460">
@@ -12839,11 +12839,11 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G460" t="n">
-        <v>0.6301862001419067</v>
+        <v>0.6803564429283142</v>
       </c>
     </row>
     <row r="461">
@@ -12866,11 +12866,11 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G461" t="n">
-        <v>0.6257973909378052</v>
+        <v>0.8148259371519089</v>
       </c>
     </row>
     <row r="462">
@@ -12893,11 +12893,11 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G462" t="n">
-        <v>0.3891035616397858</v>
+        <v>0.8148259371519089</v>
       </c>
     </row>
     <row r="463">
@@ -12920,11 +12920,11 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G463" t="n">
-        <v>0.2624373733997345</v>
+        <v>0.8148259371519089</v>
       </c>
     </row>
     <row r="464">
@@ -12947,11 +12947,11 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G464" t="n">
-        <v>0.5991654992103577</v>
+        <v>0.8148259371519089</v>
       </c>
     </row>
     <row r="465">
@@ -12974,11 +12974,11 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G465" t="n">
-        <v>0.3433161377906799</v>
+        <v>0.8148259371519089</v>
       </c>
     </row>
     <row r="466">
@@ -13001,11 +13001,11 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G466" t="n">
-        <v>0.3765042722225189</v>
+        <v>0.8148259371519089</v>
       </c>
     </row>
     <row r="467">
@@ -13028,11 +13028,11 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G467" t="n">
-        <v>0.3806164860725403</v>
+        <v>0.8148259371519089</v>
       </c>
     </row>
     <row r="468">
@@ -13055,11 +13055,11 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G468" t="n">
-        <v>0.5104234218597412</v>
+        <v>0.8148259371519089</v>
       </c>
     </row>
     <row r="469">
@@ -13082,11 +13082,11 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G469" t="n">
-        <v>0.4208474457263947</v>
+        <v>0.7997750043869019</v>
       </c>
     </row>
     <row r="470">
@@ -13109,11 +13109,11 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G470" t="n">
-        <v>0.4891553819179535</v>
+        <v>0.7997750043869019</v>
       </c>
     </row>
     <row r="471">
@@ -13136,11 +13136,11 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G471" t="n">
-        <v>0.2356323748826981</v>
+        <v>0.7997750043869019</v>
       </c>
     </row>
     <row r="472">
@@ -13163,11 +13163,11 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>0.3538668155670166</v>
+        <v>0.7997750043869019</v>
       </c>
     </row>
     <row r="473">
@@ -13190,11 +13190,11 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>0.3387757837772369</v>
+        <v>0.7997750043869019</v>
       </c>
     </row>
     <row r="474">
@@ -13217,11 +13217,11 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G474" t="n">
-        <v>0.2673711180686951</v>
+        <v>0.7997750043869019</v>
       </c>
     </row>
     <row r="475">
@@ -13244,11 +13244,11 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G475" t="n">
-        <v>0.2411248385906219</v>
+        <v>0.7997750043869019</v>
       </c>
     </row>
     <row r="476">
@@ -13271,11 +13271,11 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G476" t="n">
-        <v>0.2017453759908676</v>
+        <v>0.7997750043869019</v>
       </c>
     </row>
     <row r="477">
@@ -13298,11 +13298,11 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G477" t="n">
-        <v>0.2438661754131317</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="478">
@@ -13325,11 +13325,11 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>0.2839287221431732</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="479">
@@ -13352,11 +13352,11 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>0.256970077753067</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="480">
@@ -13379,11 +13379,11 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G480" t="n">
-        <v>0.256970077753067</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="481">
@@ -13406,11 +13406,11 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G481" t="n">
-        <v>0.256970077753067</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="482">
@@ -13433,11 +13433,11 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G482" t="n">
-        <v>0.256970077753067</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="483">
@@ -13460,11 +13460,11 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G483" t="n">
-        <v>0.256970077753067</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="484">
@@ -13487,11 +13487,11 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G484" t="n">
-        <v>0.256970077753067</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="485">
@@ -13514,11 +13514,11 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G485" t="n">
-        <v>0.256970077753067</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="486">
@@ -13541,11 +13541,11 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G486" t="n">
-        <v>0.3630572855472565</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="487">
@@ -13568,11 +13568,11 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>0.5199697613716125</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="488">
@@ -13595,11 +13595,11 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G488" t="n">
-        <v>0.4855195581912994</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="489">
@@ -13622,11 +13622,11 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G489" t="n">
-        <v>0.6112954616546631</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="490">
@@ -13649,11 +13649,11 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G490" t="n">
-        <v>0.6369179487228394</v>
+        <v>0.8697008341550827</v>
       </c>
     </row>
     <row r="491">
@@ -13676,11 +13676,11 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G491" t="n">
-        <v>0.7256655097007751</v>
+        <v>0.7501846551895142</v>
       </c>
     </row>
     <row r="492">
@@ -13703,11 +13703,11 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>0.6804046630859375</v>
+        <v>0.7501846551895142</v>
       </c>
     </row>
     <row r="493">
@@ -13730,11 +13730,11 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G493" t="n">
-        <v>0.5524234175682068</v>
+        <v>0.7501846551895142</v>
       </c>
     </row>
     <row r="494">
@@ -13757,11 +13757,11 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>0.5297034978866577</v>
+        <v>0.7501846551895142</v>
       </c>
     </row>
     <row r="495">
@@ -13784,11 +13784,11 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G495" t="n">
-        <v>0.5008568167686462</v>
+        <v>0.7501846551895142</v>
       </c>
     </row>
     <row r="496">
@@ -13811,11 +13811,11 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G496" t="n">
-        <v>0.3663502037525177</v>
+        <v>0.7501846551895142</v>
       </c>
     </row>
     <row r="497">
@@ -13838,11 +13838,11 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G497" t="n">
-        <v>0.4550469219684601</v>
+        <v>0.7501846551895142</v>
       </c>
     </row>
     <row r="498">
@@ -13865,11 +13865,11 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G498" t="n">
-        <v>0.4276564717292786</v>
+        <v>0.7501846551895142</v>
       </c>
     </row>
     <row r="499">
@@ -13892,11 +13892,11 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G499" t="n">
-        <v>0.3886217176914215</v>
+        <v>0.8767137452960014</v>
       </c>
     </row>
     <row r="500">
@@ -13919,11 +13919,11 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>Vandalism</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G500" t="n">
-        <v>0.5639508366584778</v>
+        <v>0.8767137452960014</v>
       </c>
     </row>
     <row r="501">
@@ -13946,11 +13946,11 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G501" t="n">
-        <v>0.2817589044570923</v>
+        <v>0.8767137452960014</v>
       </c>
     </row>
     <row r="502">
@@ -13973,11 +13973,11 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G502" t="n">
-        <v>0.2424915134906769</v>
+        <v>0.8767137452960014</v>
       </c>
     </row>
     <row r="503">
@@ -14000,11 +14000,11 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G503" t="n">
-        <v>0.2187770158052444</v>
+        <v>0.8767137452960014</v>
       </c>
     </row>
     <row r="504">
@@ -14027,11 +14027,11 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G504" t="n">
-        <v>0.2326407879590988</v>
+        <v>0.8767137452960014</v>
       </c>
     </row>
     <row r="505">
@@ -14054,11 +14054,11 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G505" t="n">
-        <v>0.2136091440916061</v>
+        <v>0.8767137452960014</v>
       </c>
     </row>
     <row r="506">
@@ -14081,11 +14081,11 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G506" t="n">
-        <v>0.2053939998149872</v>
+        <v>0.8767137452960014</v>
       </c>
     </row>
     <row r="507">
@@ -14108,11 +14108,11 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G507" t="n">
-        <v>0.2083419412374496</v>
+        <v>0.9829146569813232</v>
       </c>
     </row>
     <row r="508">
@@ -14135,11 +14135,11 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G508" t="n">
-        <v>0.1999084651470184</v>
+        <v>0.9829146569813232</v>
       </c>
     </row>
     <row r="509">
@@ -14162,11 +14162,11 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G509" t="n">
-        <v>0.1867088973522186</v>
+        <v>0.9829146569813232</v>
       </c>
     </row>
     <row r="510">
@@ -14189,11 +14189,11 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G510" t="n">
-        <v>0.2561094462871552</v>
+        <v>0.9829146569813232</v>
       </c>
     </row>
     <row r="511">
@@ -14216,11 +14216,11 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G511" t="n">
-        <v>0.2663222551345825</v>
+        <v>0.9829146569813232</v>
       </c>
     </row>
     <row r="512">
@@ -14243,11 +14243,11 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G512" t="n">
-        <v>0.2140007168054581</v>
+        <v>0.9829146569813232</v>
       </c>
     </row>
     <row r="513">
@@ -14270,11 +14270,11 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G513" t="n">
-        <v>0.2129461318254471</v>
+        <v>0.9829146569813232</v>
       </c>
     </row>
     <row r="514">
@@ -14297,11 +14297,11 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G514" t="n">
-        <v>0.2939340770244598</v>
+        <v>0.9829146569813232</v>
       </c>
     </row>
     <row r="515">
@@ -14324,11 +14324,11 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G515" t="n">
-        <v>0.3912425339221954</v>
+        <v>0.9770360076047306</v>
       </c>
     </row>
     <row r="516">
@@ -14351,11 +14351,11 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G516" t="n">
-        <v>0.5224302411079407</v>
+        <v>0.9770360076047306</v>
       </c>
     </row>
     <row r="517">
@@ -14378,11 +14378,11 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G517" t="n">
-        <v>0.5268459916114807</v>
+        <v>0.9770360076047306</v>
       </c>
     </row>
     <row r="518">
@@ -14405,11 +14405,11 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G518" t="n">
-        <v>0.3721916973590851</v>
+        <v>0.9770360076047306</v>
       </c>
     </row>
     <row r="519">
@@ -14432,11 +14432,11 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G519" t="n">
-        <v>0.2797724008560181</v>
+        <v>0.9770360076047306</v>
       </c>
     </row>
     <row r="520">
@@ -14459,11 +14459,11 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G520" t="n">
-        <v>0.2446334660053253</v>
+        <v>0.9770360076047306</v>
       </c>
     </row>
     <row r="521">
@@ -14486,11 +14486,11 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G521" t="n">
-        <v>0.2135714888572693</v>
+        <v>0.9770360076047306</v>
       </c>
     </row>
     <row r="522">
@@ -14513,11 +14513,11 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G522" t="n">
-        <v>0.216118261218071</v>
+        <v>0.9770360076047306</v>
       </c>
     </row>
     <row r="523">
@@ -14540,11 +14540,11 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G523" t="n">
-        <v>0.2304016798734665</v>
+        <v>0.7350299656391144</v>
       </c>
     </row>
     <row r="524">
@@ -14567,11 +14567,11 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G524" t="n">
-        <v>0.2407363653182983</v>
+        <v>0.7350299656391144</v>
       </c>
     </row>
     <row r="525">
@@ -14594,11 +14594,11 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G525" t="n">
-        <v>0.3264969885349274</v>
+        <v>0.7350299656391144</v>
       </c>
     </row>
     <row r="526">
@@ -14621,11 +14621,11 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G526" t="n">
-        <v>0.2819325029850006</v>
+        <v>0.7350299656391144</v>
       </c>
     </row>
     <row r="527">
@@ -14648,11 +14648,11 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G527" t="n">
-        <v>0.2404907196760178</v>
+        <v>0.7350299656391144</v>
       </c>
     </row>
     <row r="528">
@@ -14675,11 +14675,11 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G528" t="n">
-        <v>0.3105209767818451</v>
+        <v>0.7350299656391144</v>
       </c>
     </row>
     <row r="529">
@@ -14702,11 +14702,11 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G529" t="n">
-        <v>0.3366790413856506</v>
+        <v>0.7350299656391144</v>
       </c>
     </row>
     <row r="530">
@@ -14729,11 +14729,11 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G530" t="n">
-        <v>0.1679524779319763</v>
+        <v>0.7350299656391144</v>
       </c>
     </row>
     <row r="531">
@@ -14756,11 +14756,11 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G531" t="n">
-        <v>0.1548466831445694</v>
+        <v>0.6967492401599884</v>
       </c>
     </row>
     <row r="532">
@@ -14783,11 +14783,11 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G532" t="n">
-        <v>0.1863280385732651</v>
+        <v>0.6967492401599884</v>
       </c>
     </row>
     <row r="533">
@@ -14810,11 +14810,11 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G533" t="n">
-        <v>0.2047803997993469</v>
+        <v>0.6967492401599884</v>
       </c>
     </row>
     <row r="534">
@@ -14837,11 +14837,11 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G534" t="n">
-        <v>0.2665641009807587</v>
+        <v>0.6967492401599884</v>
       </c>
     </row>
     <row r="535">
@@ -14864,11 +14864,11 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G535" t="n">
-        <v>0.1737078577280045</v>
+        <v>0.6967492401599884</v>
       </c>
     </row>
     <row r="536">
@@ -14891,11 +14891,11 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G536" t="n">
-        <v>0.2460614293813705</v>
+        <v>0.6967492401599884</v>
       </c>
     </row>
     <row r="537">
@@ -14918,11 +14918,11 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G537" t="n">
-        <v>0.2130192518234253</v>
+        <v>0.6967492401599884</v>
       </c>
     </row>
     <row r="538">
@@ -14945,11 +14945,11 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G538" t="n">
-        <v>0.2722064256668091</v>
+        <v>0.6967492401599884</v>
       </c>
     </row>
     <row r="539">
@@ -14972,11 +14972,11 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G539" t="n">
-        <v>0.5015513896942139</v>
+        <v>0.8692108541727066</v>
       </c>
     </row>
     <row r="540">
@@ -14999,11 +14999,11 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G540" t="n">
-        <v>0.409119039773941</v>
+        <v>0.8692108541727066</v>
       </c>
     </row>
     <row r="541">
@@ -15026,11 +15026,11 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G541" t="n">
-        <v>0.2282838523387909</v>
+        <v>0.8692108541727066</v>
       </c>
     </row>
     <row r="542">
@@ -15053,11 +15053,11 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G542" t="n">
-        <v>0.3114313185214996</v>
+        <v>0.8692108541727066</v>
       </c>
     </row>
     <row r="543">
@@ -15080,11 +15080,11 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G543" t="n">
-        <v>0.3439337909221649</v>
+        <v>0.8692108541727066</v>
       </c>
     </row>
     <row r="544">
@@ -15107,11 +15107,11 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G544" t="n">
-        <v>0.3205378949642181</v>
+        <v>0.8692108541727066</v>
       </c>
     </row>
     <row r="545">
@@ -15134,11 +15134,11 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G545" t="n">
-        <v>0.4188763499259949</v>
+        <v>0.8692108541727066</v>
       </c>
     </row>
     <row r="546">
@@ -15161,11 +15161,11 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G546" t="n">
-        <v>0.4590463638305664</v>
+        <v>0.8692108541727066</v>
       </c>
     </row>
     <row r="547">
@@ -15188,11 +15188,11 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G547" t="n">
-        <v>0.5397967100143433</v>
+        <v>0.573270171880722</v>
       </c>
     </row>
     <row r="548">
@@ -15215,11 +15215,11 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G548" t="n">
-        <v>0.4982641637325287</v>
+        <v>0.573270171880722</v>
       </c>
     </row>
     <row r="549">
@@ -15242,11 +15242,11 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G549" t="n">
-        <v>0.7074030637741089</v>
+        <v>0.573270171880722</v>
       </c>
     </row>
     <row r="550">
@@ -15269,11 +15269,11 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G550" t="n">
-        <v>0.4845952391624451</v>
+        <v>0.573270171880722</v>
       </c>
     </row>
     <row r="551">
@@ -15296,11 +15296,11 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G551" t="n">
-        <v>0.465594470500946</v>
+        <v>0.573270171880722</v>
       </c>
     </row>
     <row r="552">
@@ -15323,11 +15323,11 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G552" t="n">
-        <v>0.2900944650173187</v>
+        <v>0.573270171880722</v>
       </c>
     </row>
     <row r="553">
@@ -15350,11 +15350,11 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G553" t="n">
-        <v>0.3184849321842194</v>
+        <v>0.573270171880722</v>
       </c>
     </row>
     <row r="554">
@@ -15377,11 +15377,11 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G554" t="n">
-        <v>0.2756617069244385</v>
+        <v>0.573270171880722</v>
       </c>
     </row>
     <row r="555">
@@ -15404,11 +15404,11 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G555" t="n">
-        <v>0.2676188945770264</v>
+        <v>0.3615110516548157</v>
       </c>
     </row>
     <row r="556">
@@ -15431,11 +15431,11 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G556" t="n">
-        <v>0.2677746415138245</v>
+        <v>0.3615110516548157</v>
       </c>
     </row>
     <row r="557">
@@ -15458,11 +15458,11 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G557" t="n">
-        <v>0.3670942485332489</v>
+        <v>0.3615110516548157</v>
       </c>
     </row>
     <row r="558">
@@ -15485,11 +15485,11 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G558" t="n">
-        <v>0.2895253598690033</v>
+        <v>0.3615110516548157</v>
       </c>
     </row>
     <row r="559">
@@ -15512,11 +15512,11 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G559" t="n">
-        <v>0.2574403285980225</v>
+        <v>0.3615110516548157</v>
       </c>
     </row>
     <row r="560">
@@ -15539,11 +15539,11 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Explosion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G560" t="n">
-        <v>0.2710832059383392</v>
+        <v>0.3615110516548157</v>
       </c>
     </row>
     <row r="561">
@@ -15566,11 +15566,11 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G561" t="n">
-        <v>0.3030261695384979</v>
+        <v>0.3615110516548157</v>
       </c>
     </row>
     <row r="562">
@@ -15593,11 +15593,11 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G562" t="n">
-        <v>0.2812289595603943</v>
+        <v>0.3615110516548157</v>
       </c>
     </row>
     <row r="563">
@@ -15620,11 +15620,11 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G563" t="n">
-        <v>0.3230438232421875</v>
+        <v>0.6722486615180969</v>
       </c>
     </row>
     <row r="564">
@@ -15647,11 +15647,11 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G564" t="n">
-        <v>0.3436767756938934</v>
+        <v>0.6722486615180969</v>
       </c>
     </row>
     <row r="565">
@@ -15674,11 +15674,11 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G565" t="n">
-        <v>0.2477013468742371</v>
+        <v>0.6722486615180969</v>
       </c>
     </row>
     <row r="566">
@@ -15701,11 +15701,11 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G566" t="n">
-        <v>0.2969282567501068</v>
+        <v>0.6722486615180969</v>
       </c>
     </row>
     <row r="567">
@@ -15728,11 +15728,11 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G567" t="n">
-        <v>0.272542804479599</v>
+        <v>0.6722486615180969</v>
       </c>
     </row>
     <row r="568">
@@ -15755,11 +15755,11 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G568" t="n">
-        <v>0.2730581760406494</v>
+        <v>0.6722486615180969</v>
       </c>
     </row>
     <row r="569">
@@ -15782,11 +15782,11 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G569" t="n">
-        <v>0.2974586188793182</v>
+        <v>0.6722486615180969</v>
       </c>
     </row>
     <row r="570">
@@ -15809,11 +15809,11 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G570" t="n">
-        <v>0.2628965377807617</v>
+        <v>0.6722486615180969</v>
       </c>
     </row>
     <row r="571">
@@ -15836,11 +15836,11 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G571" t="n">
-        <v>0.3067494332790375</v>
+        <v>0.7766571342945099</v>
       </c>
     </row>
     <row r="572">
@@ -15863,11 +15863,11 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G572" t="n">
-        <v>0.3637150824069977</v>
+        <v>0.7766571342945099</v>
       </c>
     </row>
     <row r="573">
@@ -15890,11 +15890,11 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G573" t="n">
-        <v>0.3139224052429199</v>
+        <v>0.7766571342945099</v>
       </c>
     </row>
     <row r="574">
@@ -15917,11 +15917,11 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G574" t="n">
-        <v>0.455088198184967</v>
+        <v>0.7766571342945099</v>
       </c>
     </row>
     <row r="575">
@@ -15944,11 +15944,11 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G575" t="n">
-        <v>0.3538180887699127</v>
+        <v>0.7766571342945099</v>
       </c>
     </row>
     <row r="576">
@@ -15971,11 +15971,11 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G576" t="n">
-        <v>0.416198343038559</v>
+        <v>0.7766571342945099</v>
       </c>
     </row>
     <row r="577">
@@ -15998,11 +15998,11 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G577" t="n">
-        <v>0.7935293912887573</v>
+        <v>0.7766571342945099</v>
       </c>
     </row>
     <row r="578">
@@ -16025,11 +16025,11 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G578" t="n">
-        <v>0.902374804019928</v>
+        <v>0.7766571342945099</v>
       </c>
     </row>
     <row r="579">
@@ -16052,11 +16052,11 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G579" t="n">
-        <v>0.9235481023788452</v>
+        <v>0.5300518274307251</v>
       </c>
     </row>
     <row r="580">
@@ -16079,11 +16079,11 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G580" t="n">
-        <v>0.917629063129425</v>
+        <v>0.5300518274307251</v>
       </c>
     </row>
     <row r="581">
@@ -16106,11 +16106,11 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G581" t="n">
-        <v>0.8631015419960022</v>
+        <v>0.5300518274307251</v>
       </c>
     </row>
     <row r="582">
@@ -16133,11 +16133,11 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G582" t="n">
-        <v>0.8297231197357178</v>
+        <v>0.5300518274307251</v>
       </c>
     </row>
     <row r="583">
@@ -16160,11 +16160,11 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G583" t="n">
-        <v>0.8185365200042725</v>
+        <v>0.5300518274307251</v>
       </c>
     </row>
     <row r="584">
@@ -16187,11 +16187,11 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G584" t="n">
-        <v>0.8021054267883301</v>
+        <v>0.5300518274307251</v>
       </c>
     </row>
     <row r="585">
@@ -16214,11 +16214,11 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G585" t="n">
-        <v>0.7097828388214111</v>
+        <v>0.5300518274307251</v>
       </c>
     </row>
     <row r="586">
@@ -16241,11 +16241,11 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Burglary</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G586" t="n">
-        <v>0.349002480506897</v>
+        <v>0.5300518274307251</v>
       </c>
     </row>
     <row r="587">
@@ -16268,11 +16268,11 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Vandalism</t>
         </is>
       </c>
       <c r="G587" t="n">
-        <v>0.5927789211273193</v>
+        <v>0.6907453536987305</v>
       </c>
     </row>
     <row r="588">
@@ -16295,11 +16295,11 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Vandalism</t>
         </is>
       </c>
       <c r="G588" t="n">
-        <v>0.5187056064605713</v>
+        <v>0.6907453536987305</v>
       </c>
     </row>
     <row r="589">
@@ -16322,11 +16322,11 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Vandalism</t>
         </is>
       </c>
       <c r="G589" t="n">
-        <v>0.5114176273345947</v>
+        <v>0.6907453536987305</v>
       </c>
     </row>
     <row r="590">
@@ -16349,11 +16349,11 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Vandalism</t>
         </is>
       </c>
       <c r="G590" t="n">
-        <v>0.4807151257991791</v>
+        <v>0.6907453536987305</v>
       </c>
     </row>
     <row r="591">
@@ -16376,11 +16376,11 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Vandalism</t>
         </is>
       </c>
       <c r="G591" t="n">
-        <v>0.4642617404460907</v>
+        <v>0.6907453536987305</v>
       </c>
     </row>
     <row r="592">
@@ -16403,11 +16403,11 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Vandalism</t>
         </is>
       </c>
       <c r="G592" t="n">
-        <v>0.3894185125827789</v>
+        <v>0.6907453536987305</v>
       </c>
     </row>
     <row r="593">
@@ -16430,11 +16430,11 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Vandalism</t>
         </is>
       </c>
       <c r="G593" t="n">
-        <v>0.4824530482292175</v>
+        <v>0.6907453536987305</v>
       </c>
     </row>
     <row r="594">
@@ -16457,11 +16457,11 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Vandalism</t>
         </is>
       </c>
       <c r="G594" t="n">
-        <v>0.4154399335384369</v>
+        <v>0.6907453536987305</v>
       </c>
     </row>
     <row r="595">
@@ -16484,11 +16484,11 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G595" t="n">
-        <v>0.3813433945178986</v>
+        <v>0.7110765278339386</v>
       </c>
     </row>
     <row r="596">
@@ -16511,11 +16511,11 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>0.3131738305091858</v>
+        <v>0.7110765278339386</v>
       </c>
     </row>
     <row r="597">
@@ -16538,11 +16538,11 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G597" t="n">
-        <v>0.3439002335071564</v>
+        <v>0.7110765278339386</v>
       </c>
     </row>
     <row r="598">
@@ -16565,11 +16565,11 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>0.3791210949420929</v>
+        <v>0.7110765278339386</v>
       </c>
     </row>
     <row r="599">
@@ -16592,11 +16592,11 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G599" t="n">
-        <v>0.329680323600769</v>
+        <v>0.7110765278339386</v>
       </c>
     </row>
     <row r="600">
@@ -16619,11 +16619,11 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G600" t="n">
-        <v>0.3289321660995483</v>
+        <v>0.7110765278339386</v>
       </c>
     </row>
     <row r="601">
@@ -16646,11 +16646,11 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G601" t="n">
-        <v>0.2925454378128052</v>
+        <v>0.7110765278339386</v>
       </c>
     </row>
     <row r="602">
@@ -16673,11 +16673,11 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G602" t="n">
-        <v>0.3557434678077698</v>
+        <v>0.7110765278339386</v>
       </c>
     </row>
     <row r="603">
@@ -16700,11 +16700,11 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G603" t="n">
-        <v>0.2783597111701965</v>
+        <v>0.9126999452710152</v>
       </c>
     </row>
     <row r="604">
@@ -16727,11 +16727,11 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G604" t="n">
-        <v>0.560345470905304</v>
+        <v>0.9126999452710152</v>
       </c>
     </row>
     <row r="605">
@@ -16754,11 +16754,11 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G605" t="n">
-        <v>0.5147474408149719</v>
+        <v>0.9126999452710152</v>
       </c>
     </row>
     <row r="606">
@@ -16781,11 +16781,11 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G606" t="n">
-        <v>0.499972939491272</v>
+        <v>0.9126999452710152</v>
       </c>
     </row>
     <row r="607">
@@ -16808,11 +16808,11 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G607" t="n">
-        <v>0.4276133477687836</v>
+        <v>0.9126999452710152</v>
       </c>
     </row>
     <row r="608">
@@ -16835,11 +16835,11 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G608" t="n">
-        <v>0.3894588053226471</v>
+        <v>0.9126999452710152</v>
       </c>
     </row>
     <row r="609">
@@ -16862,11 +16862,11 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G609" t="n">
-        <v>0.3805217444896698</v>
+        <v>0.9126999452710152</v>
       </c>
     </row>
     <row r="610">
@@ -16889,11 +16889,11 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G610" t="n">
-        <v>0.3058826923370361</v>
+        <v>0.9126999452710152</v>
       </c>
     </row>
     <row r="611">
@@ -16916,11 +16916,11 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G611" t="n">
-        <v>0.3087988495826721</v>
+        <v>0.8951373398303986</v>
       </c>
     </row>
     <row r="612">
@@ -16943,11 +16943,11 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G612" t="n">
-        <v>0.3852296471595764</v>
+        <v>0.8951373398303986</v>
       </c>
     </row>
     <row r="613">
@@ -16970,11 +16970,11 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G613" t="n">
-        <v>0.3423483967781067</v>
+        <v>0.8951373398303986</v>
       </c>
     </row>
     <row r="614">
@@ -16997,11 +16997,11 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G614" t="n">
-        <v>0.5179343223571777</v>
+        <v>0.8951373398303986</v>
       </c>
     </row>
     <row r="615">
@@ -17024,11 +17024,11 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G615" t="n">
-        <v>0.359912246465683</v>
+        <v>0.8951373398303986</v>
       </c>
     </row>
     <row r="616">
@@ -17051,11 +17051,11 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G616" t="n">
-        <v>0.4190364181995392</v>
+        <v>0.8951373398303986</v>
       </c>
     </row>
     <row r="617">
@@ -17078,11 +17078,11 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G617" t="n">
-        <v>0.6059286594390869</v>
+        <v>0.8951373398303986</v>
       </c>
     </row>
     <row r="618">
@@ -17105,11 +17105,11 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G618" t="n">
-        <v>0.677910327911377</v>
+        <v>0.8951373398303986</v>
       </c>
     </row>
     <row r="619">
@@ -17132,11 +17132,11 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G619" t="n">
-        <v>0.7023270726203918</v>
+        <v>0.5880298614501953</v>
       </c>
     </row>
     <row r="620">
@@ -17159,11 +17159,11 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G620" t="n">
-        <v>0.6197242140769958</v>
+        <v>0.5880298614501953</v>
       </c>
     </row>
     <row r="621">
@@ -17186,11 +17186,11 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G621" t="n">
-        <v>0.6082690954208374</v>
+        <v>0.5880298614501953</v>
       </c>
     </row>
     <row r="622">
@@ -17213,11 +17213,11 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G622" t="n">
-        <v>0.3934597671031952</v>
+        <v>0.5880298614501953</v>
       </c>
     </row>
     <row r="623">
@@ -17240,11 +17240,11 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G623" t="n">
-        <v>0.4338461458683014</v>
+        <v>0.5880298614501953</v>
       </c>
     </row>
     <row r="624">
@@ -17267,11 +17267,11 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G624" t="n">
-        <v>0.408464103937149</v>
+        <v>0.5880298614501953</v>
       </c>
     </row>
     <row r="625">
@@ -17294,11 +17294,11 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G625" t="n">
-        <v>0.4336634874343872</v>
+        <v>0.5880298614501953</v>
       </c>
     </row>
     <row r="626">
@@ -17321,11 +17321,11 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G626" t="n">
-        <v>0.5596712827682495</v>
+        <v>0.5880298614501953</v>
       </c>
     </row>
     <row r="627">
@@ -17348,11 +17348,11 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G627" t="n">
-        <v>0.4779705703258514</v>
+        <v>0.7072352468967438</v>
       </c>
     </row>
     <row r="628">
@@ -17375,11 +17375,11 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G628" t="n">
-        <v>0.4757658839225769</v>
+        <v>0.7072352468967438</v>
       </c>
     </row>
     <row r="629">
@@ -17402,11 +17402,11 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G629" t="n">
-        <v>0.4984760284423828</v>
+        <v>0.7072352468967438</v>
       </c>
     </row>
     <row r="630">
@@ -17429,11 +17429,11 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G630" t="n">
-        <v>0.4975816607475281</v>
+        <v>0.7072352468967438</v>
       </c>
     </row>
     <row r="631">
@@ -17456,11 +17456,11 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G631" t="n">
-        <v>0.3848423361778259</v>
+        <v>0.7072352468967438</v>
       </c>
     </row>
     <row r="632">
@@ -17483,11 +17483,11 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G632" t="n">
-        <v>0.436801016330719</v>
+        <v>0.7072352468967438</v>
       </c>
     </row>
     <row r="633">
@@ -17510,11 +17510,11 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G633" t="n">
-        <v>0.4163404405117035</v>
+        <v>0.7072352468967438</v>
       </c>
     </row>
     <row r="634">
@@ -17537,11 +17537,11 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G634" t="n">
-        <v>0.3291865587234497</v>
+        <v>0.7072352468967438</v>
       </c>
     </row>
     <row r="635">
@@ -17564,11 +17564,11 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G635" t="n">
-        <v>0.2923460006713867</v>
+        <v>0.9852761366133641</v>
       </c>
     </row>
     <row r="636">
@@ -17591,11 +17591,11 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G636" t="n">
-        <v>0.3838756680488586</v>
+        <v>0.9852761366133641</v>
       </c>
     </row>
     <row r="637">
@@ -17618,11 +17618,11 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G637" t="n">
-        <v>0.3058490753173828</v>
+        <v>0.9852761366133641</v>
       </c>
     </row>
     <row r="638">
@@ -17645,11 +17645,11 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G638" t="n">
-        <v>0.4293333292007446</v>
+        <v>0.9852761366133641</v>
       </c>
     </row>
     <row r="639">
@@ -17672,11 +17672,11 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G639" t="n">
-        <v>0.427140861749649</v>
+        <v>0.9852761366133641</v>
       </c>
     </row>
     <row r="640">
@@ -17699,11 +17699,11 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G640" t="n">
-        <v>0.4654543399810791</v>
+        <v>0.9852761366133641</v>
       </c>
     </row>
     <row r="641">
@@ -17726,11 +17726,11 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G641" t="n">
-        <v>0.4093135893344879</v>
+        <v>0.9852761366133641</v>
       </c>
     </row>
     <row r="642">
@@ -17753,11 +17753,11 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G642" t="n">
-        <v>0.3925846815109253</v>
+        <v>0.9852761366133641</v>
       </c>
     </row>
     <row r="643">
@@ -17780,11 +17780,11 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G643" t="n">
-        <v>0.3461744785308838</v>
+        <v>0.9765652009804575</v>
       </c>
     </row>
     <row r="644">
@@ -17807,11 +17807,11 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G644" t="n">
-        <v>0.3206848502159119</v>
+        <v>0.9765652009804575</v>
       </c>
     </row>
     <row r="645">
@@ -17834,11 +17834,11 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G645" t="n">
-        <v>0.3577685058116913</v>
+        <v>0.9765652009804575</v>
       </c>
     </row>
     <row r="646">
@@ -17861,11 +17861,11 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G646" t="n">
-        <v>0.4310807883739471</v>
+        <v>0.9765652009804575</v>
       </c>
     </row>
     <row r="647">
@@ -17888,11 +17888,11 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G647" t="n">
-        <v>0.371224969625473</v>
+        <v>0.9765652009804575</v>
       </c>
     </row>
     <row r="648">
@@ -17915,11 +17915,11 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G648" t="n">
-        <v>0.4132393002510071</v>
+        <v>0.9765652009804575</v>
       </c>
     </row>
     <row r="649">
@@ -17942,11 +17942,11 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G649" t="n">
-        <v>0.4207212626934052</v>
+        <v>0.9765652009804575</v>
       </c>
     </row>
     <row r="650">
@@ -17969,11 +17969,11 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G650" t="n">
-        <v>0.6756988763809204</v>
+        <v>0.9765652009804575</v>
       </c>
     </row>
     <row r="651">
@@ -17996,11 +17996,11 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G651" t="n">
-        <v>0.6430973410606384</v>
+        <v>0.8677388876676559</v>
       </c>
     </row>
     <row r="652">
@@ -18023,11 +18023,11 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G652" t="n">
-        <v>0.4906316995620728</v>
+        <v>0.8677388876676559</v>
       </c>
     </row>
     <row r="653">
@@ -18050,11 +18050,11 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G653" t="n">
-        <v>0.3996737599372864</v>
+        <v>0.8677388876676559</v>
       </c>
     </row>
     <row r="654">
@@ -18077,11 +18077,11 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G654" t="n">
-        <v>0.4716498255729675</v>
+        <v>0.8677388876676559</v>
       </c>
     </row>
     <row r="655">
@@ -18104,11 +18104,11 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G655" t="n">
-        <v>0.5146552920341492</v>
+        <v>0.8677388876676559</v>
       </c>
     </row>
     <row r="656">
@@ -18131,11 +18131,11 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G656" t="n">
-        <v>0.4766547679901123</v>
+        <v>0.8677388876676559</v>
       </c>
     </row>
     <row r="657">
@@ -18158,11 +18158,11 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G657" t="n">
-        <v>0.4790475964546204</v>
+        <v>0.8677388876676559</v>
       </c>
     </row>
     <row r="658">
@@ -18185,11 +18185,11 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G658" t="n">
-        <v>0.6989439129829407</v>
+        <v>0.8677388876676559</v>
       </c>
     </row>
     <row r="659">
@@ -18212,11 +18212,11 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G659" t="n">
-        <v>0.7987990379333496</v>
+        <v>0.958658080548048</v>
       </c>
     </row>
     <row r="660">
@@ -18239,11 +18239,11 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G660" t="n">
-        <v>0.8095498085021973</v>
+        <v>0.958658080548048</v>
       </c>
     </row>
     <row r="661">
@@ -18266,11 +18266,11 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G661" t="n">
-        <v>0.8316057920455933</v>
+        <v>0.958658080548048</v>
       </c>
     </row>
     <row r="662">
@@ -18293,11 +18293,11 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G662" t="n">
-        <v>0.8164402842521667</v>
+        <v>0.958658080548048</v>
       </c>
     </row>
     <row r="663">
@@ -18320,11 +18320,11 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G663" t="n">
-        <v>0.6696328520774841</v>
+        <v>0.958658080548048</v>
       </c>
     </row>
     <row r="664">
@@ -18347,11 +18347,11 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G664" t="n">
-        <v>0.5653873682022095</v>
+        <v>0.958658080548048</v>
       </c>
     </row>
     <row r="665">
@@ -18374,11 +18374,11 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G665" t="n">
-        <v>0.5997717380523682</v>
+        <v>0.958658080548048</v>
       </c>
     </row>
     <row r="666">
@@ -18401,11 +18401,11 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G666" t="n">
-        <v>0.7946224808692932</v>
+        <v>0.958658080548048</v>
       </c>
     </row>
     <row r="667">
@@ -18428,11 +18428,11 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G667" t="n">
-        <v>0.7305253744125366</v>
+        <v>0.9875973761081696</v>
       </c>
     </row>
     <row r="668">
@@ -18455,11 +18455,11 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G668" t="n">
-        <v>0.7348177433013916</v>
+        <v>0.9875973761081696</v>
       </c>
     </row>
     <row r="669">
@@ -18482,11 +18482,11 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G669" t="n">
-        <v>0.6041733622550964</v>
+        <v>0.9875973761081696</v>
       </c>
     </row>
     <row r="670">
@@ -18509,11 +18509,11 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G670" t="n">
-        <v>0.5418438315391541</v>
+        <v>0.9875973761081696</v>
       </c>
     </row>
     <row r="671">
@@ -18536,11 +18536,11 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G671" t="n">
-        <v>0.4563959538936615</v>
+        <v>0.9875973761081696</v>
       </c>
     </row>
     <row r="672">
@@ -18563,11 +18563,11 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G672" t="n">
-        <v>0.501146137714386</v>
+        <v>0.9875973761081696</v>
       </c>
     </row>
     <row r="673">
@@ -18590,11 +18590,11 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G673" t="n">
-        <v>0.5086931586265564</v>
+        <v>0.9875973761081696</v>
       </c>
     </row>
     <row r="674">
@@ -18617,11 +18617,11 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G674" t="n">
-        <v>0.3263979554176331</v>
+        <v>0.9875973761081696</v>
       </c>
     </row>
     <row r="675">
@@ -18644,11 +18644,11 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G675" t="n">
-        <v>0.3769815266132355</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
     <row r="676">
@@ -18671,11 +18671,11 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G676" t="n">
-        <v>0.4505874812602997</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
     <row r="677">
@@ -18698,11 +18698,11 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G677" t="n">
-        <v>0.4842097759246826</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
     <row r="678">
@@ -18725,11 +18725,11 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>RoadAccidents</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G678" t="n">
-        <v>0.4738749861717224</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
     <row r="679">
@@ -18752,11 +18752,11 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G679" t="n">
-        <v>0.49394890666008</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
     <row r="680">
@@ -18779,11 +18779,11 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G680" t="n">
-        <v>0.438842386007309</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
     <row r="681">
@@ -18806,11 +18806,11 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G681" t="n">
-        <v>0.622974693775177</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
     <row r="682">
@@ -18833,11 +18833,11 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G682" t="n">
-        <v>0.4605426788330078</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
     <row r="683">
@@ -18860,11 +18860,11 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>0.4605426788330078</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
     <row r="684">
@@ -18887,11 +18887,11 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G684" t="n">
-        <v>0.4605426788330078</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
     <row r="685">
@@ -18914,11 +18914,11 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>0.4605426788330078</v>
+        <v>0.9856749707832932</v>
       </c>
     </row>
   </sheetData>
